--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_09-09-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_09-09-2025.xlsx
@@ -518,17 +518,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -898,17 +898,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1884,17 +1884,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
